--- a/frontend/public/test-data/master_student_users_test_data.xlsx
+++ b/frontend/public/test-data/master_student_users_test_data.xlsx
@@ -470,7 +470,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>083msncs03@pcampus.edu.np</v>
+        <v>083msice01@pcampus.edu.np</v>
       </c>
       <c r="B4" t="str">
         <v>Test@123</v>
@@ -482,10 +482,10 @@
         <v>Kumal</v>
       </c>
       <c r="E4" t="str">
-        <v>083MSNCS03</v>
+        <v>083MSICE01</v>
       </c>
       <c r="F4" t="str">
-        <v>MSNCS</v>
+        <v>MSICE</v>
       </c>
       <c r="G4" t="str">
         <v>MASTER</v>
@@ -493,7 +493,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>083msncs04@pcampus.edu.np</v>
+        <v>083msice02@pcampus.edu.np</v>
       </c>
       <c r="B5" t="str">
         <v>Test@123</v>
@@ -505,10 +505,10 @@
         <v>Timalsina</v>
       </c>
       <c r="E5" t="str">
-        <v>083MSNCS04</v>
+        <v>083MSICE02</v>
       </c>
       <c r="F5" t="str">
-        <v>MSNCS</v>
+        <v>MSICE</v>
       </c>
       <c r="G5" t="str">
         <v>MASTER</v>
@@ -516,7 +516,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>083msncs05@pcampus.edu.np</v>
+        <v>083msdsa01@pcampus.edu.np</v>
       </c>
       <c r="B6" t="str">
         <v>Test@123</v>
@@ -528,10 +528,10 @@
         <v>Dangol</v>
       </c>
       <c r="E6" t="str">
-        <v>083MSNCS05</v>
+        <v>083MSDSA01</v>
       </c>
       <c r="F6" t="str">
-        <v>MSNCS</v>
+        <v>MSDSA</v>
       </c>
       <c r="G6" t="str">
         <v>MASTER</v>
@@ -539,7 +539,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>083msncs06@pcampus.edu.np</v>
+        <v>083msdsa02@pcampus.edu.np</v>
       </c>
       <c r="B7" t="str">
         <v>Test@123</v>
@@ -551,10 +551,10 @@
         <v>Acharya</v>
       </c>
       <c r="E7" t="str">
-        <v>083MSNCS06</v>
+        <v>083MSDSA02</v>
       </c>
       <c r="F7" t="str">
-        <v>MSNCS</v>
+        <v>MSDSA</v>
       </c>
       <c r="G7" t="str">
         <v>MASTER</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>083msncs07@pcampus.edu.np</v>
+        <v>083mscsk01@pcampus.edu.np</v>
       </c>
       <c r="B8" t="str">
         <v>Test@123</v>
@@ -574,10 +574,10 @@
         <v>Dahal</v>
       </c>
       <c r="E8" t="str">
-        <v>083MSNCS07</v>
+        <v>083MSCSK01</v>
       </c>
       <c r="F8" t="str">
-        <v>MSNCS</v>
+        <v>MSCSK</v>
       </c>
       <c r="G8" t="str">
         <v>MASTER</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>083msncs08@pcampus.edu.np</v>
+        <v>083mscsk02@pcampus.edu.np</v>
       </c>
       <c r="B9" t="str">
         <v>Test@123</v>
@@ -597,10 +597,10 @@
         <v>Lama</v>
       </c>
       <c r="E9" t="str">
-        <v>083MSNCS08</v>
+        <v>083MSCSK02</v>
       </c>
       <c r="F9" t="str">
-        <v>MSNCS</v>
+        <v>MSCSK</v>
       </c>
       <c r="G9" t="str">
         <v>MASTER</v>
